--- a/warships.xlsx
+++ b/warships.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>序号</t>
   </si>
@@ -115,10 +115,37 @@
     <t>诡计号</t>
   </si>
   <si>
-    <t>小型帆船</t>
-  </si>
-  <si>
-    <t>殉爆（自身被击沉时，对周围3*3区域所有船只造成1点伤害）</t>
+    <t>殉爆（被动，自身被击沉时，对周围3*3区域所有船只造成1点伤害）</t>
+  </si>
+  <si>
+    <t>黄泉号</t>
+  </si>
+  <si>
+    <t>铁甲（被动，船舷每次受到的撞击和舷炮伤害-1，但每回合最多前进两次。一轮舷炮多枚同时命中视作受到一次伤害）</t>
+  </si>
+  <si>
+    <t>火力增强（被动，舷炮射程＋1）</t>
+  </si>
+  <si>
+    <t>屠夫号</t>
+  </si>
+  <si>
+    <t>布雷（主动，消耗1点行动力，在棋子周围一圈10格中选择一个空格布下水雷。任何船只以任何位移经过水雷格都会引爆，受到1点伤害。每局可使用3次）</t>
+  </si>
+  <si>
+    <t>舜臣号</t>
+  </si>
+  <si>
+    <t>龟船防御（被动，舜臣号不携带舷炮，但自身承受的撞击伤害-1）</t>
+  </si>
+  <si>
+    <t>乌尔卡号</t>
+  </si>
+  <si>
+    <t>补给（主动，消耗1点行动力，为与自己接舷的一艘友方舰船回复1点生命，每局可使用2次）</t>
+  </si>
+  <si>
+    <t>弹药支援（主动，自身舷炮存在时可使用，消耗1点行动力，移除自身舷炮，为与自己接舷的一艘友方舰船补充一次舷炮）</t>
   </si>
 </sst>
 </file>
@@ -835,7 +862,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14280515" y="431800"/>
+          <a:off x="14415135" y="431800"/>
           <a:ext cx="384810" cy="268605"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -877,7 +904,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="14382750" y="1641475"/>
+          <a:off x="14517370" y="1641475"/>
           <a:ext cx="252095" cy="379095"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1195,7 +1222,7 @@
     <col min="3" max="3" width="10.3703703703704" customWidth="1"/>
     <col min="4" max="4" width="9.11111111111111" customWidth="1"/>
     <col min="5" max="5" width="110.481481481481" customWidth="1"/>
-    <col min="6" max="6" width="51" customWidth="1"/>
+    <col min="6" max="6" width="52.962962962963" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6">
@@ -1357,19 +1384,89 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:6">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
       </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="10" ht="28" customHeight="1"/>
-    <row r="11" ht="28" customHeight="1"/>
-    <row r="12" ht="28" customHeight="1"/>
-    <row r="13" ht="28" customHeight="1"/>
+    <row r="11" ht="28" customHeight="1" spans="1:6">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:6">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:6">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="14" ht="28" customHeight="1"/>
     <row r="15" ht="28" customHeight="1"/>
     <row r="16" ht="28" customHeight="1"/>

--- a/warships.xlsx
+++ b/warships.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8616"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -142,7 +142,7 @@
     <t>乌尔卡号</t>
   </si>
   <si>
-    <t>补给（主动，消耗1点行动力，为与自己接舷的一艘友方舰船回复1点生命，每局可使用2次）</t>
+    <t>补给（主动，消耗1点行动力，为与自己接舷的一艘友方舰船回复1点生命，每局可使用3次）</t>
   </si>
   <si>
     <t>弹药支援（主动，自身舷炮存在时可使用，消耗1点行动力，移除自身舷炮，为与自己接舷的一艘友方舰船补充一次舷炮）</t>
